--- a/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
+++ b/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\BSfVBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BSfVBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9D6FEB-034F-478A-8AD8-D0B136B65BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F63064-E60C-4E0D-89A3-031CD1AE0005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59685" yWindow="1425" windowWidth="21495" windowHeight="15210" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -753,57 +753,75 @@
         <v>6.4364923393820792</v>
       </c>
       <c r="N2">
+        <f>$E2*(1-About!$A$14)^(N1-$E1)*'Phase Out'!L3</f>
         <v>0</v>
       </c>
       <c r="O2">
+        <f>$E2*(1-About!$A$14)^(O1-$E1)*'Phase Out'!M3</f>
         <v>0</v>
       </c>
       <c r="P2">
+        <f>$E2*(1-About!$A$14)^(P1-$E1)*'Phase Out'!N3</f>
         <v>0</v>
       </c>
       <c r="Q2">
+        <f>$E2*(1-About!$A$14)^(Q1-$E1)*'Phase Out'!O3</f>
         <v>0</v>
       </c>
       <c r="R2">
+        <f>$E2*(1-About!$A$14)^(R1-$E1)*'Phase Out'!P3</f>
         <v>0</v>
       </c>
       <c r="S2">
+        <f>$E2*(1-About!$A$14)^(S1-$E1)*'Phase Out'!Q3</f>
         <v>0</v>
       </c>
       <c r="T2">
+        <f>$E2*(1-About!$A$14)^(T1-$E1)*'Phase Out'!R3</f>
         <v>0</v>
       </c>
       <c r="U2">
+        <f>$E2*(1-About!$A$14)^(U1-$E1)*'Phase Out'!S3</f>
         <v>0</v>
       </c>
       <c r="V2">
+        <f>$E2*(1-About!$A$14)^(V1-$E1)*'Phase Out'!T3</f>
         <v>0</v>
       </c>
       <c r="W2">
+        <f>$E2*(1-About!$A$14)^(W1-$E1)*'Phase Out'!U3</f>
         <v>0</v>
       </c>
       <c r="X2">
+        <f>$E2*(1-About!$A$14)^(X1-$E1)*'Phase Out'!V3</f>
         <v>0</v>
       </c>
       <c r="Y2">
+        <f>$E2*(1-About!$A$14)^(Y1-$E1)*'Phase Out'!W3</f>
         <v>0</v>
       </c>
       <c r="Z2">
+        <f>$E2*(1-About!$A$14)^(Z1-$E1)*'Phase Out'!X3</f>
         <v>0</v>
       </c>
       <c r="AA2">
+        <f>$E2*(1-About!$A$14)^(AA1-$E1)*'Phase Out'!Y3</f>
         <v>0</v>
       </c>
       <c r="AB2">
+        <f>$E2*(1-About!$A$14)^(AB1-$E1)*'Phase Out'!Z3</f>
         <v>0</v>
       </c>
       <c r="AC2">
+        <f>$E2*(1-About!$A$14)^(AC1-$E1)*'Phase Out'!AA3</f>
         <v>0</v>
       </c>
       <c r="AD2">
+        <f>$E2*(1-About!$A$14)^(AD1-$E1)*'Phase Out'!AB3</f>
         <v>0</v>
       </c>
       <c r="AE2">
+        <f>$E2*(1-About!$A$14)^(AE1-$E1)*'Phase Out'!AC3</f>
         <v>0</v>
       </c>
     </row>
